--- a/test_data/mercury_pro_gripper.xlsx
+++ b/test_data/mercury_pro_gripper.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="2" activeTab="14"/>
+    <workbookView windowWidth="27948" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="get_pro_gripper" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="49">
   <si>
     <t>ID</t>
   </si>
@@ -58,12 +58,24 @@
     <t>expect_data</t>
   </si>
   <si>
+    <t>test_type</t>
+  </si>
+  <si>
     <t>正确获取夹爪参数</t>
   </si>
   <si>
     <t>get_pro_gripper</t>
   </si>
   <si>
+    <t>normal</t>
+  </si>
+  <si>
+    <t>获取夹爪参数超限</t>
+  </si>
+  <si>
+    <t>exception</t>
+  </si>
+  <si>
     <t>正确获取夹爪角度</t>
   </si>
   <si>
@@ -73,9 +85,6 @@
     <t>正确获取夹爪速度</t>
   </si>
   <si>
-    <t>test_type</t>
-  </si>
-  <si>
     <t>获取夹爪运动时的夹持状态</t>
   </si>
   <si>
@@ -100,9 +109,6 @@
     <t>set_pro_gripper</t>
   </si>
   <si>
-    <t>normal</t>
-  </si>
-  <si>
     <t>正确设置夹爪绝对运动</t>
   </si>
   <si>
@@ -116,9 +122,6 @@
   </si>
   <si>
     <t>设置绝对运动角度（超限）</t>
-  </si>
-  <si>
-    <t>exception</t>
   </si>
   <si>
     <t>正确设置夹爪角度(100度)</t>
@@ -1118,8 +1121,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="4"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
     <col min="3" max="3" width="19.4444444444444" customWidth="1"/>
@@ -1127,7 +1130,7 @@
     <col min="5" max="5" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1143,57 +1146,252 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:6">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1">
-        <v>21</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="1">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1">
+        <v>22</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="1">
-        <v>23</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1">
+        <v>24</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>26</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8">
+        <v>34</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9">
+        <v>35</v>
+      </c>
+      <c r="E9">
         <v>0</v>
       </c>
+      <c r="F9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10">
+        <v>40</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11">
+        <v>42</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12">
+        <v>44</v>
+      </c>
+      <c r="E12">
+        <v>300</v>
+      </c>
+      <c r="F12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13">
+        <v>45</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="1"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1237,10 +1435,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -1285,10 +1483,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -1333,10 +1531,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -1380,7 +1578,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:6">
@@ -1388,10 +1586,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1">
         <v>100</v>
@@ -1400,7 +1598,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:6">
@@ -1408,16 +1606,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="D3" s="1">
         <v>101</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:6">
@@ -1425,16 +1623,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1475,10 +1673,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -1520,7 +1718,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="28" customHeight="1" spans="1:6">
@@ -1528,10 +1726,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D2" s="1">
         <v>10</v>
@@ -1540,7 +1738,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="28.8" spans="1:6">
@@ -1548,16 +1746,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="D3" s="1">
         <v>255</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
@@ -1565,16 +1763,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1617,10 +1815,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -1668,10 +1866,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -1716,7 +1914,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="45" customHeight="1" spans="1:6">
@@ -1724,10 +1922,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -1741,10 +1939,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1">
         <v>1</v>
@@ -1753,15 +1951,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="43.2" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1">
         <v>2</v>
@@ -1770,15 +1968,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="43.2" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="E5" s="1">
         <v>3</v>
@@ -1805,7 +2003,7 @@
     <col min="5" max="6" width="15.5555555555556" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:7">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1819,13 +2017,13 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1833,10 +2031,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1">
         <v>21</v>
@@ -1848,7 +2046,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1856,10 +2054,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D3">
         <v>22</v>
@@ -1871,7 +2069,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1879,10 +2077,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D4">
         <v>23</v>
@@ -1894,7 +2092,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1928,13 +2126,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="28.8" spans="1:6">
@@ -1942,10 +2140,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D2" s="1">
         <v>50</v>
@@ -1962,10 +2160,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E3" s="1">
         <v>1</v>
@@ -1979,10 +2177,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
@@ -1996,16 +2194,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D5" s="1">
         <v>101</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2039,13 +2237,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="28.8" spans="1:6">
@@ -2053,10 +2251,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1">
         <v>100</v>
@@ -2065,7 +2263,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="28.8" spans="1:6">
@@ -2073,10 +2271,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -2085,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
@@ -2093,16 +2291,16 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4" s="1">
         <v>101</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2146,10 +2344,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -2197,10 +2395,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">

--- a/test_data/mercury_pro_gripper.xlsx
+++ b/test_data/mercury_pro_gripper.xlsx
@@ -1224,7 +1224,7 @@
         <v>22</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
         <v>8</v>
@@ -1244,7 +1244,7 @@
         <v>24</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>8</v>
@@ -1304,7 +1304,7 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
         <v>8</v>
@@ -1364,7 +1364,7 @@
         <v>44</v>
       </c>
       <c r="E12">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F12" t="s">
         <v>8</v>

--- a/test_data/mercury_pro_gripper.xlsx
+++ b/test_data/mercury_pro_gripper.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300"/>
+    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="10" activeTab="15"/>
   </bookViews>
   <sheets>
     <sheet name="get_pro_gripper" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="set_pro_gripper_speed" sheetId="13" r:id="rId13"/>
     <sheet name="set_pro_gripper_stop" sheetId="14" r:id="rId14"/>
     <sheet name="set_pro_gripper_torque" sheetId="15" r:id="rId15"/>
+    <sheet name="get_pro_gripper_torque" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="51">
   <si>
     <t>ID</t>
   </si>
@@ -188,6 +189,12 @@
   </si>
   <si>
     <t>设置夹爪扭矩（超限）</t>
+  </si>
+  <si>
+    <t>获取夹爪扭矩</t>
+  </si>
+  <si>
+    <t>get_gripper_torque</t>
   </si>
 </sst>
 </file>
@@ -1304,7 +1311,7 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F9" t="s">
         <v>8</v>
@@ -1344,7 +1351,7 @@
         <v>42</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
         <v>8</v>
@@ -1773,6 +1780,61 @@
       </c>
       <c r="F4" s="1" t="s">
         <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="8.88888888888889" style="1"/>
+    <col min="2" max="2" width="21.7777777777778" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.7777777777778" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88888888888889" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="28" customHeight="1" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="1">
+        <v>300</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/test_data/mercury_pro_gripper.xlsx
+++ b/test_data/mercury_pro_gripper.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="10" activeTab="15"/>
+    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="4" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="get_pro_gripper" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="52">
   <si>
     <t>ID</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>set_pro_gripper</t>
+  </si>
+  <si>
+    <t>设置夹爪参数超限</t>
   </si>
   <si>
     <t>正确设置夹爪绝对运动</t>
@@ -1442,10 +1445,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -1490,10 +1493,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -1538,10 +1541,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -1593,10 +1596,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" s="1">
         <v>100</v>
@@ -1613,10 +1616,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="D3" s="1">
         <v>101</v>
@@ -1630,10 +1633,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -1680,10 +1683,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -1733,10 +1736,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D2" s="1">
         <v>10</v>
@@ -1753,10 +1756,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="D3" s="1">
         <v>255</v>
@@ -1770,10 +1773,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -1825,13 +1828,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E2" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -2056,8 +2059,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
     <col min="3" max="3" width="19.4444444444444" customWidth="1"/>
@@ -2099,10 +2102,10 @@
         <v>21</v>
       </c>
       <c r="D2" s="1">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
@@ -2122,10 +2125,10 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -2145,16 +2148,322 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>23</v>
+      </c>
+      <c r="E5">
+        <v>14</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6">
+        <v>25</v>
+      </c>
+      <c r="E6">
+        <v>150</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7">
+        <v>30</v>
+      </c>
+      <c r="E7">
+        <v>80</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8">
+        <v>31</v>
+      </c>
+      <c r="E8">
+        <v>50</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9">
+        <v>41</v>
+      </c>
+      <c r="E9">
+        <v>77</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10">
+        <v>43</v>
+      </c>
+      <c r="E10">
+        <v>230</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="1">
+        <v>10</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="1">
+        <v>21</v>
+      </c>
+      <c r="E12" s="1">
+        <v>17</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="1">
+        <v>23</v>
+      </c>
+      <c r="E13" s="1">
+        <v>17</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="1">
+        <v>25</v>
+      </c>
+      <c r="E14" s="1">
+        <v>255</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="1">
+        <v>30</v>
+      </c>
+      <c r="E15" s="1">
+        <v>101</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="1">
+        <v>31</v>
+      </c>
+      <c r="E16" s="1">
+        <v>101</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="1">
+        <v>41</v>
+      </c>
+      <c r="E17" s="1">
+        <v>101</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="1">
+        <v>43</v>
+      </c>
+      <c r="E18" s="1">
+        <v>255</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2202,10 +2511,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" s="1">
         <v>50</v>
@@ -2222,10 +2531,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="E3" s="1">
         <v>1</v>
@@ -2239,10 +2548,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
@@ -2256,10 +2565,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1">
         <v>101</v>
@@ -2313,10 +2622,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1">
         <v>100</v>
@@ -2333,10 +2642,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -2353,10 +2662,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1">
         <v>101</v>
@@ -2406,10 +2715,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -2457,10 +2766,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">

--- a/test_data/mercury_pro_gripper.xlsx
+++ b/test_data/mercury_pro_gripper.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="4" activeTab="4"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="4" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="get_pro_gripper" sheetId="1" r:id="rId1"/>
@@ -2459,7 +2459,7 @@
         <v>43</v>
       </c>
       <c r="E18" s="1">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" t="s">

--- a/test_data/mercury_pro_gripper.xlsx
+++ b/test_data/mercury_pro_gripper.xlsx
@@ -2459,7 +2459,7 @@
         <v>43</v>
       </c>
       <c r="E18" s="1">
-        <v>256</v>
+        <v>301</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" t="s">

--- a/test_data/mercury_pro_gripper.xlsx
+++ b/test_data/mercury_pro_gripper.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="4" activeTab="4"/>
+    <workbookView windowWidth="24750" windowHeight="11870" firstSheet="8" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="get_pro_gripper" sheetId="1" r:id="rId1"/>
@@ -173,7 +173,7 @@
     <t>正确设置夹爪速度</t>
   </si>
   <si>
-    <t>set_speed</t>
+    <t>set_pro_gripper_speed</t>
   </si>
   <si>
     <t>设置夹爪速度（超限）</t>
@@ -1132,12 +1132,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="19.4444444444444" customWidth="1"/>
-    <col min="4" max="4" width="15.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="21.7818181818182" customWidth="1"/>
+    <col min="3" max="3" width="19.4454545454545" customWidth="1"/>
+    <col min="4" max="4" width="15.5545454545455" customWidth="1"/>
+    <col min="5" max="5" width="14.7818181818182" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1234,7 +1234,7 @@
         <v>22</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
         <v>8</v>
@@ -1254,7 +1254,7 @@
         <v>24</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
         <v>8</v>
@@ -1274,7 +1274,7 @@
         <v>26</v>
       </c>
       <c r="E7">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
@@ -1294,7 +1294,7 @@
         <v>34</v>
       </c>
       <c r="E8">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F8" t="s">
         <v>8</v>
@@ -1314,7 +1314,7 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F9" t="s">
         <v>8</v>
@@ -1354,7 +1354,7 @@
         <v>42</v>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="F11" t="s">
         <v>8</v>
@@ -1374,7 +1374,7 @@
         <v>44</v>
       </c>
       <c r="E12">
-        <v>297</v>
+        <v>255</v>
       </c>
       <c r="F12" t="s">
         <v>8</v>
@@ -1414,13 +1414,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.5555555555556" customWidth="1"/>
-    <col min="2" max="2" width="27.1111111111111" customWidth="1"/>
-    <col min="3" max="3" width="24.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="13.4444444444444" customWidth="1"/>
-    <col min="5" max="5" width="13.2222222222222" customWidth="1"/>
+    <col min="1" max="1" width="13.5545454545455" customWidth="1"/>
+    <col min="2" max="2" width="27.1090909090909" customWidth="1"/>
+    <col min="3" max="3" width="24.5545454545455" customWidth="1"/>
+    <col min="4" max="4" width="13.4454545454545" customWidth="1"/>
+    <col min="5" max="5" width="13.2181818181818" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1465,13 +1465,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="21.7818181818182" customWidth="1"/>
+    <col min="3" max="3" width="24.7818181818182" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:5">
+    <row r="1" ht="28" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1513,13 +1513,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="21.7818181818182" customWidth="1"/>
+    <col min="3" max="3" width="24.7818181818182" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:5">
+    <row r="1" ht="28" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1561,17 +1561,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" style="1"/>
-    <col min="2" max="2" width="21.7777777777778" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" style="1" customWidth="1"/>
-    <col min="4" max="5" width="8.88888888888889" style="1"/>
-    <col min="6" max="6" width="12.7777777777778" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="8.89090909090909" style="1"/>
+    <col min="2" max="2" width="21.7818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.7818181818182" style="1" customWidth="1"/>
+    <col min="4" max="5" width="8.89090909090909" style="1"/>
+    <col min="6" max="6" width="12.7818181818182" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.89090909090909" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1655,13 +1655,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="21.7818181818182" customWidth="1"/>
+    <col min="3" max="3" width="24.7818181818182" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:5">
+    <row r="1" ht="28" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1703,15 +1703,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" style="1"/>
-    <col min="2" max="2" width="21.7777777777778" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="8.89090909090909" style="1"/>
+    <col min="2" max="2" width="21.7818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.7818181818182" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.89090909090909" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1795,15 +1795,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" style="1"/>
-    <col min="2" max="2" width="21.7777777777778" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="8.89090909090909" style="1"/>
+    <col min="2" max="2" width="21.7818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.7818181818182" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.89090909090909" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1850,12 +1850,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="19.4444444444444" customWidth="1"/>
-    <col min="4" max="4" width="15.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="21.7818181818182" customWidth="1"/>
+    <col min="3" max="3" width="19.4454545454545" customWidth="1"/>
+    <col min="4" max="4" width="15.5545454545455" customWidth="1"/>
+    <col min="5" max="5" width="14.7818181818182" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1901,12 +1901,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="19.4444444444444" customWidth="1"/>
-    <col min="4" max="4" width="15.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="21.7818181818182" customWidth="1"/>
+    <col min="3" max="3" width="19.4454545454545" customWidth="1"/>
+    <col min="4" max="4" width="15.5545454545455" customWidth="1"/>
+    <col min="5" max="5" width="14.7818181818182" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1952,13 +1952,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.4444444444444" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7777777777778" style="1" customWidth="1"/>
-    <col min="4" max="5" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.4444444444444" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.4454545454545" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7818181818182" style="1" customWidth="1"/>
+    <col min="4" max="5" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.4454545454545" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1999,7 +1999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -2060,12 +2060,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="19.4444444444444" customWidth="1"/>
-    <col min="4" max="4" width="14.5555555555556" customWidth="1"/>
-    <col min="5" max="6" width="15.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="21.7818181818182" customWidth="1"/>
+    <col min="3" max="3" width="19.4454545454545" customWidth="1"/>
+    <col min="4" max="4" width="14.5545454545455" customWidth="1"/>
+    <col min="5" max="6" width="15.5545454545455" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2476,17 +2476,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" style="1"/>
-    <col min="2" max="2" width="21.7777777777778" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" style="1" customWidth="1"/>
-    <col min="4" max="5" width="8.88888888888889" style="1"/>
-    <col min="6" max="6" width="12.6666666666667" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="8.89090909090909" style="1"/>
+    <col min="2" max="2" width="21.7818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.7818181818182" style="1" customWidth="1"/>
+    <col min="4" max="5" width="8.89090909090909" style="1"/>
+    <col min="6" max="6" width="12.6636363636364" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.89090909090909" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2506,7 +2506,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="2" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2543,7 +2543,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -2587,17 +2587,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.1111111111111" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.8888888888889" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.4444444444444" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.2222222222222" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="13.5545454545455" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.1090909090909" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.8909090909091" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.4454545454545" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.2181818181818" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.89090909090909" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="2" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2657,7 +2657,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A4" s="1">
         <v>4</v>
       </c>
@@ -2684,13 +2684,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.5555555555556" customWidth="1"/>
-    <col min="2" max="2" width="27.1111111111111" customWidth="1"/>
-    <col min="3" max="3" width="24.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="13.4444444444444" customWidth="1"/>
-    <col min="5" max="5" width="13.2222222222222" customWidth="1"/>
+    <col min="1" max="1" width="13.5545454545455" customWidth="1"/>
+    <col min="2" max="2" width="27.1090909090909" customWidth="1"/>
+    <col min="3" max="3" width="24.5545454545455" customWidth="1"/>
+    <col min="4" max="4" width="13.4454545454545" customWidth="1"/>
+    <col min="5" max="5" width="13.2181818181818" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2735,13 +2735,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.5555555555556" customWidth="1"/>
-    <col min="2" max="2" width="27.1111111111111" customWidth="1"/>
-    <col min="3" max="3" width="24.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="13.4444444444444" customWidth="1"/>
-    <col min="5" max="5" width="13.2222222222222" customWidth="1"/>
+    <col min="1" max="1" width="13.5545454545455" customWidth="1"/>
+    <col min="2" max="2" width="27.1090909090909" customWidth="1"/>
+    <col min="3" max="3" width="24.5545454545455" customWidth="1"/>
+    <col min="4" max="4" width="13.4454545454545" customWidth="1"/>
+    <col min="5" max="5" width="13.2181818181818" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
